--- a/reports/Debug-purgatory-20260105/Month to Date (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/Month to Date (Prior Year)_Revenue.xlsx
@@ -106,16 +106,16 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
     <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
-  </si>
-  <si>
-    <t>T101</t>
   </si>
   <si>
     <t>department</t>
@@ -570,7 +570,8 @@
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -598,7 +599,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="2">
-        <v>11205.00</v>
+        <v>300.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -612,7 +613,7 @@
         <v>35</v>
       </c>
       <c r="D3" s="2">
-        <v>380.62</v>
+        <v>394109.43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -626,7 +627,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>14007.00</v>
+        <v>6167.42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -640,7 +641,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="2">
-        <v>1038777.01</v>
+        <v>69.50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -654,7 +655,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="2">
-        <v>413458.97</v>
+        <v>5626.00</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -786,7 +787,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="2">
-        <v>3811.44</v>
+        <v>3800.00</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -930,7 +931,7 @@
         <v>58</v>
       </c>
       <c r="D29" s="2">
-        <v>2401.10</v>
+        <v>1952.88</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -942,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="D30" s="2">
-        <v>3441.30</v>
+        <v>2216.52</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -954,7 +955,7 @@
         <v>60</v>
       </c>
       <c r="D31" s="2">
-        <v>17508.17</v>
+        <v>1977.86</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -966,7 +967,7 @@
         <v>61</v>
       </c>
       <c r="D32" s="2">
-        <v>8906.64</v>
+        <v>5776.89</v>
       </c>
     </row>
   </sheetData>
